--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -851,10 +851,8 @@
           <t>Tek Raj Bhattarai</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861431231</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861431231</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -889,10 +887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.672145</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.672145</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +944,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.282233</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.28223300000001</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1062,10 +1054,8 @@
           <t>Krishna kumar basnet</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9849335487</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9849335487</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1155,10 +1145,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1169,7 +1157,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1265,10 +1253,8 @@
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843863828</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843863828</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1303,10 +1289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.656438</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.656438</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1358,48 +1342,466 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.374787</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.374787</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>20h 49m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>20h 49m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>only one light in router</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9861431231</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9861431231</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:47:24 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.672145</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Panga Near Panga Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>9848851796||bhattarairaj685@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.282233</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343660</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Kanchhi Tamang</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Kanchhi Tamang</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9843863828</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9843863828</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:18:01 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.656438</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near Sirutar khadhka gau,Bhaktapur Municipality, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>tamangrayal51@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>07:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.374787</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 42m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1416,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1453,7 +1855,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1463,7 +1865,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1474,7 +1876,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1900,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 26m</t>
+          <t>23h 42m</t>
         </is>
       </c>
     </row>
@@ -1539,14 +1941,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1557,10 +1959,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1615,14 +2017,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1638,10 +2040,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1757,7 +2159,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1824,14 +2226,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>24 Sep 2026 09:33:03 AM</t>
@@ -1855,6 +2257,140 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>20h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:47:24 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 43m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343660</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Kanchhi Tamang</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:18:01 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:00:43 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>21h 42m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1452,10 +1452,8 @@
           <t>Tek Raj Bhattarai</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9861431231</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9861431231</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1490,10 +1488,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.672145</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.672145</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1549,25 +1545,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.282233</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.28223300000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1663,10 +1655,8 @@
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9843863828</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9843863828</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1701,10 +1691,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.656438</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.656438</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1760,25 +1748,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.374787</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.374787</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1827,7 +1811,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2293,7 +2277,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2360,7 +2344,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -512,27 +512,27 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1788,6 +1788,627 @@
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343646</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Manik lal Yadav</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Manik lal Yadav</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813427907</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:23:55 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9813427907</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:18:34 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>test123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>54m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343059</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31:16 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:50:55 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:31:16 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 40m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Res light in stb</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343880</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:04:09 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.74341</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Maharajganj Near Banglamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.33884</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 21m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1802,11 +2423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1839,7 +2460,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1860,7 +2481,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1943,436 +2564,500 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343214</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Tek Raj Bhattarai</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 08:04:03 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 07:30:34 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:46:58 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 42m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1343714</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Krishna kumar basnet</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:57:02 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>20h 36m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343214</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Tek Raj Bhattarai</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 08:04:03 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 07:30:34 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:47:24 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 43m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:46:58 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 42m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343714</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Krishna kumar basnet</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:33:03 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:57:02 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:33:03 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>20h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:47:24 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 43m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1343660</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:18:01 PM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>21h 42m</t>
         </is>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1858,10 +1858,8 @@
           <t>Manik lal Yadav</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813427907</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813427907</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1896,10 +1894,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1951,25 +1947,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2065,10 +2057,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2103,10 +2093,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2158,25 +2146,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2272,10 +2256,8 @@
           <t>Avishek Satyal</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9843171373</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9843171373</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2310,10 +2292,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.74341</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.74341</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2347,10 +2327,8 @@
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr"/>
       <c r="AJ9" s="3" t="inlineStr"/>
@@ -2365,48 +2343,462 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.33884</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.33884</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 21m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343489</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9862062974</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 12:41:41 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>BKT9862062974</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:43:55 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:43:45 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Nrw thimi, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>Test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>22h 2m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 59m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>No light on router</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344041</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9843304328</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9843304328</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:16:21 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.670306</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Khwopa Engineering College, Libali-2, Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>mee.lone28@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>03:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L17-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.439137</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>19h 21m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2423,7 +2815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2432,7 +2824,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2460,7 +2852,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2470,7 +2862,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2493,7 +2885,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 51m</t>
+          <t>10h 17m</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2897,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 42m</t>
+          <t>22h 27m</t>
         </is>
       </c>
     </row>
@@ -2564,10 +2956,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2686,26 +3078,26 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2720,167 +3112,123 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1343214</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Tek Raj Bhattarai</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 08:04:03 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 07:30:34 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:46:58 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>1d 1h 42m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1343714</t>
+          <t>TKT1343214</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Krishna kumar basnet</t>
+          <t>Tek Raj Bhattarai</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2900,64 +3248,64 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
+          <t>23 Sep 2026 08:04:03 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:57:02 PM</t>
+          <t>23 Sep 2026 07:30:34 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
+          <t>24 Sep 2026 09:46:58 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 42m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>20h 36m</t>
+          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1343214</t>
+          <t>TKT1343714</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Tek Raj Bhattarai</t>
+          <t>Krishna kumar basnet</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2967,99 +3315,233 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 08:04:03 AM</t>
+          <t>24 Sep 2026 09:33:03 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 07:30:34 AM</t>
+          <t>23 Sep 2026 12:57:02 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 09:47:24 AM</t>
+          <t>24 Sep 2026 09:33:03 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 16m</t>
+          <t>20h 36m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1343214</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tek Raj Bhattarai</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:04:03 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:30:34 AM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:47:24 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 43m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1343660</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Kanchhi Tamang</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026 12:18:01 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>21h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344041</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:16:21 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2453,10 +2453,8 @@
           <t>Indra rai</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9862062974</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9862062974</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2491,10 +2489,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2546,25 +2542,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2660,10 +2652,8 @@
           <t>Milan Suwal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9843304328</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9843304328</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2698,10 +2688,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.670306</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.670306</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2757,50 +2745,245 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L17-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.439137</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.439137</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>17h 25m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:48 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343458</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:48:31 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>M7CH+6J8 Kirtipur 44600,NEAR Panga Bus Park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>nigambakhariya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2824,7 +3007,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2852,7 +3035,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2873,7 +3056,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -2938,14 +3121,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3032,14 +3215,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3694,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2855,10 +2855,8 @@
           <t>Nigam Bakhariya</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9869216939</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9869216939</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2944,10 +2942,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -2958,7 +2954,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2978,6 +2978,635 @@
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344159</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9842788566</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9842788566</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:24:41 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.68512</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>near by Danphe Chari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>prabeshuprety1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>02:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3314</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>16h 26m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344035</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9818106969</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:10:05 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841865344</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:10:05 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:13:19 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.67843</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Advance oral dental hospital Saraswati Marga, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>neekitaupadhyay5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3465</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>18h 3m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>18h 3m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343797</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Anish Pradhan</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Anish Pradhan</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9860428234</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9860428234</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:09:53 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.672004</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>SallaGhari Near By Nepal Skin Bhaktapur,01, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>pradhananish4@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>06:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.409664</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>20h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2994,7 +3623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3003,7 +3632,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3031,7 +3660,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3041,7 +3670,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3052,7 +3681,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3693,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 17m</t>
+          <t>7h 20m</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3705,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 27m</t>
+          <t>21h 23m</t>
         </is>
       </c>
     </row>
@@ -3117,14 +3746,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -3211,14 +3840,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -3721,6 +4350,140 @@
       <c r="M28" s="3" t="inlineStr">
         <is>
           <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344159</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:24:41 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>16h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343797</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Anish Pradhan</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:09:53 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:08:35 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>20h 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3050,10 +3050,8 @@
           <t>Bhishma Uprety</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9842788566</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9842788566</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3088,10 +3086,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.68512</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.68512</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3147,25 +3143,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3314</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.3314</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3261,10 +3253,8 @@
           <t>Nikita Upadhaya</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9818106969</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9818106969</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3299,10 +3289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.67843</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.67843</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3354,25 +3342,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3465</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.34650000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3468,10 +3452,8 @@
           <t>Anish Pradhan</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9860428234</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9860428234</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3506,10 +3488,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.672004</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.672004</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3565,25 +3545,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.409664</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.40966400000001</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3632,7 +3608,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4386,7 +4362,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -4453,7 +4429,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3583,6 +3583,428 @@
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344272</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Anil Aryal</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Anil Aryal</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849610463</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849610463</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:09:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali kharibot , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>test123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>02:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB472</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>15h 11m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344220</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Samir Subedi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Samir Subedi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9813870559</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9813870559</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:15:25 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.715676</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bhairab Road Nayabasti, Gokarneshwor ward no:6,near Kumari Bhairab Temple , Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L52-2</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.367613</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>15h 55m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3599,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3608,7 +4030,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3636,7 +4058,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3646,7 +4068,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3657,7 +4079,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -3669,7 +4091,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 20m</t>
+          <t>5h 42m</t>
         </is>
       </c>
     </row>
@@ -3681,7 +4103,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 23m</t>
+          <t>20h 5m</t>
         </is>
       </c>
     </row>
@@ -3722,14 +4144,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -3754,99 +4176,94 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -3858,18 +4275,18 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3881,30 +4298,30 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3919,212 +4336,124 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343214</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Tek Raj Bhattarai</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 08:04:03 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 07:30:34 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:46:58 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 42m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1343714</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Krishna kumar basnet</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>23 Sep 2026 12:57:02 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 09:33:03 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>20h 36m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4480,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4181,12 +4510,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 09:47:24 AM</t>
+          <t>24 Sep 2026 09:46:58 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 43m</t>
+          <t>1d 1h 42m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4198,12 +4527,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1343660</t>
+          <t>TKT1343714</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Kanchhi Tamang</t>
+          <t>Krishna kumar basnet</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4233,22 +4562,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 10:00:43 AM</t>
+          <t>24 Sep 2026 09:33:03 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 12:18:01 PM</t>
+          <t>23 Sep 2026 12:57:02 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 10:00:43 AM</t>
+          <t>24 Sep 2026 09:33:03 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4258,19 +4587,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>21h 42m</t>
+          <t>20h 36m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1344041</t>
+          <t>TKT1343214</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Milan Suwal</t>
+          <t>Tek Raj Bhattarai</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4285,12 +4614,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4300,44 +4629,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+          <t>Case : only one light in router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 10:41:54 AM</t>
+          <t>23 Sep 2026 08:04:03 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>23 Sep 2026 05:16:21 PM</t>
+          <t>23 Sep 2026 07:30:34 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 10:41:54 AM</t>
+          <t>24 Sep 2026 09:47:24 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 1h 43m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>17h 25m</t>
+          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1344159</t>
+          <t>TKT1343660</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Bhishma Uprety</t>
+          <t>Kanchhi Tamang</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4367,22 +4696,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 11:51:17 AM</t>
+          <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 07:24:41 PM</t>
+          <t>23 Sep 2026 12:18:01 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 11:51:17 AM</t>
+          <t>24 Sep 2026 10:00:43 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4392,74 +4721,342 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>16h 26m</t>
+          <t>21h 42m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1344041</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Milan Suwal</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light on router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:16:21 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:41:54 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>17h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344159</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bhishma Uprety</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:24:41 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:51:17 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>16h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1343797</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Anish Pradhan</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>24 Sep 2026 11:08:35 AM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 02:09:53 PM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>24 Sep 2026 11:08:35 AM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>20h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344272</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Anil Aryal</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:09:54 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:21:13 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>15h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344220</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Samir Subedi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:15:25 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:44 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>15h 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3655,10 +3655,8 @@
           <t>Anil Aryal</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849610463</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849610463</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3693,10 +3691,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3734,10 +3730,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
@@ -3756,25 +3750,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB472</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3870,10 +3860,8 @@
           <t>Samir Subedi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9813870559</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9813870559</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3908,10 +3896,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.715676</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.715676</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3963,25 +3949,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L52-2</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.367613</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.36761300000001</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4030,7 +4012,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4959,7 +4941,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -5026,7 +5008,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3987,6 +3987,205 @@
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344169</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>sabin basnet</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>sabin basnet</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9803241299</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9863542185</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:33:00 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	sankhamul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>03:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4003,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4012,7 +4211,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4040,7 +4239,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -4050,7 +4249,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4061,7 +4260,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4272,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 42m</t>
+          <t>5h 8m</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4284,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 5m</t>
+          <t>19h 49m</t>
         </is>
       </c>
     </row>
@@ -4126,14 +4325,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4238,14 +4437,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5039,6 +5238,73 @@
       <c r="M34" s="3" t="inlineStr">
         <is>
           <t>15h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344169</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>sabin basnet</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 07:33:00 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:55:27 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4059,10 +4059,8 @@
           <t>sabin basnet</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9803241299</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9803241299</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4148,10 +4146,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4162,7 +4158,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4211,7 +4207,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5274,7 +5270,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4182,6 +4182,205 @@
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344280</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Asad ul haq</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Asad ul haq</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9827815110</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9827815110</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:18:20 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:42:24 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Attarkhel Nmc chowk	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>03:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L44-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>16h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4198,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4207,7 +4406,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4235,7 +4434,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -4245,7 +4444,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4256,7 +4455,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4467,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 8m</t>
+          <t>4h 40m</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4479,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 49m</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
@@ -4321,14 +4520,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -4433,14 +4632,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -5301,6 +5500,73 @@
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>17h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344280</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Asad ul haq</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:18:20 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:42:24 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>16h 24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4254,10 +4254,8 @@
           <t>Asad ul haq</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9827815110</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9827815110</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4343,10 +4341,8 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4357,7 +4353,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4406,7 +4402,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5536,7 +5532,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4379,6 +4379,217 @@
       <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Res light in stb</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343880</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9843171373</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:04:09 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 03:47:39 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.74341</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Maharajganj Near Banglamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.33884</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 43m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4393,16 +4604,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4430,7 +4641,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4440,7 +4651,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4451,7 +4662,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4674,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 40m</t>
+          <t>4h 44m</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4686,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 30m</t>
+          <t>19h 56m</t>
         </is>
       </c>
     </row>
@@ -4534,14 +4745,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -4651,14 +4862,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5563,6 +5774,73 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>16h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343880</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Avishek Satyal</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:25:13 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:04:09 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 03:47:39 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1d 43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4449,10 +4449,8 @@
           <t>Avishek Satyal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9843171373</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9843171373</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4487,10 +4485,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.74341</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.74341</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4524,10 +4520,8 @@
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -4546,25 +4540,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.33884</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.33884</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4613,7 +4603,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5810,7 +5800,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Res light in stb  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4578,6 +4578,217 @@
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>router lost</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342385</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Seven Seas logistic</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Seven Seas logistic</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9851000248</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9851000248</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 12:49:56 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.727913</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near to Presidential Business School,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>management@7seahnepal.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>23:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB454</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.324016</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 30m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -4594,7 +4805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4603,7 +4814,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4631,7 +4842,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4641,7 +4852,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -4652,7 +4863,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4875,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 44m</t>
+          <t>4h 22m</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4887,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 56m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
@@ -4735,14 +4946,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -4898,14 +5109,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5831,6 +6042,73 @@
       <c r="M37" s="5" t="inlineStr">
         <is>
           <t>1d 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342385</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Seven Seas logistic</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 12:49:56 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:20:04 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 30m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4650,10 +4650,8 @@
           <t>Seven Seas logistic</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9851000248</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9851000248</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4688,10 +4686,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.727913</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.727913</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4747,25 +4743,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB454</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.324016</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.324016</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4814,7 +4806,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6078,7 +6070,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case :  router lost    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
